--- a/outputs/Redditch Library - Fenster Pricing Document (CLIENT COPY).xlsx
+++ b/outputs/Redditch Library - Fenster Pricing Document (CLIENT COPY).xlsx
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="H9" s="86" t="n">
-        <v>1895.63</v>
+        <v>1895.4</v>
       </c>
       <c r="I9" s="88" t="n">
-        <v>1895.63</v>
+        <v>1895.4</v>
       </c>
       <c r="J9" s="93" t="n"/>
       <c r="K9" s="4" t="n"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="H10" s="86" t="n">
-        <v>1895.63</v>
+        <v>1895.4</v>
       </c>
       <c r="I10" s="88" t="n">
-        <v>1895.63</v>
+        <v>1895.4</v>
       </c>
       <c r="J10" s="93" t="n"/>
       <c r="K10" s="4" t="n"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="H11" s="86" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="I11" s="88" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="J11" s="93" t="n"/>
       <c r="K11" s="4" t="n"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="H12" s="86" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="I12" s="88" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="J12" s="93" t="n"/>
       <c r="K12" s="4" t="n"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="H13" s="86" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="I13" s="88" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="J13" s="93" t="n"/>
       <c r="K13" s="4" t="n"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="H14" s="86" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="I14" s="88" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="J14" s="93" t="n"/>
       <c r="K14" s="4" t="n"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="H15" s="86" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="I15" s="88" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="J15" s="93" t="n"/>
       <c r="K15" s="4" t="n"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="H16" s="86" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="I16" s="88" t="n">
-        <v>2161.73</v>
+        <v>2161.46</v>
       </c>
       <c r="J16" s="93" t="n"/>
       <c r="K16" s="4" t="n"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="H17" s="86" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="I17" s="88" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="J17" s="93" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="H18" s="86" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="I18" s="88" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="J18" s="93" t="n"/>
       <c r="K18" s="4" t="n"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H19" s="86" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="I19" s="88" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="J19" s="93" t="n"/>
       <c r="K19" s="4" t="n"/>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="H20" s="101" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="I20" s="102" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="J20" s="103" t="n"/>
       <c r="K20" s="4" t="n"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="H21" s="101" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="I21" s="102" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="J21" s="103" t="n"/>
       <c r="K21" s="4" t="n"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="H22" s="101" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="I22" s="102" t="n">
-        <v>1894.85</v>
+        <v>1894.62</v>
       </c>
       <c r="J22" s="103" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H23" s="101" t="n">
-        <v>1203.48</v>
+        <v>1203.33</v>
       </c>
       <c r="I23" s="102" t="n">
-        <v>1203.48</v>
+        <v>1203.33</v>
       </c>
       <c r="J23" s="103" t="n"/>
       <c r="K23" s="4" t="n"/>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="H24" s="101" t="n">
-        <v>2249.28</v>
+        <v>2249.01</v>
       </c>
       <c r="I24" s="102" t="n">
-        <v>2249.28</v>
+        <v>2249.01</v>
       </c>
       <c r="J24" s="103" t="n"/>
       <c r="K24" s="4" t="n"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="H25" s="101" t="n">
-        <v>2249.28</v>
+        <v>2249.01</v>
       </c>
       <c r="I25" s="102" t="n">
-        <v>2249.28</v>
+        <v>2249.01</v>
       </c>
       <c r="J25" s="103" t="n"/>
       <c r="K25" s="4" t="n"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="H26" s="101" t="n">
-        <v>2249.28</v>
+        <v>2249.01</v>
       </c>
       <c r="I26" s="102" t="n">
-        <v>2249.28</v>
+        <v>2249.01</v>
       </c>
       <c r="J26" s="103" t="n"/>
       <c r="K26" s="4" t="n"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="H27" s="101" t="n">
-        <v>4114.27</v>
+        <v>4550.67</v>
       </c>
       <c r="I27" s="102" t="n">
-        <v>4114.27</v>
+        <v>4550.67</v>
       </c>
       <c r="J27" s="103" t="n"/>
       <c r="K27" s="4" t="n"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="H28" s="101" t="n">
-        <v>2806.87</v>
+        <v>3140.63</v>
       </c>
       <c r="I28" s="102" t="n">
-        <v>2806.87</v>
+        <v>3140.63</v>
       </c>
       <c r="J28" s="103" t="n"/>
       <c r="K28" s="4" t="n"/>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="H29" s="101" t="n">
-        <v>1203.48</v>
+        <v>1203.33</v>
       </c>
       <c r="I29" s="102" t="n">
-        <v>1203.48</v>
+        <v>1203.33</v>
       </c>
       <c r="J29" s="103" t="n"/>
       <c r="K29" s="4" t="n"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="H30" s="101" t="n">
-        <v>1224.38</v>
+        <v>1224.23</v>
       </c>
       <c r="I30" s="102" t="n">
-        <v>1224.38</v>
+        <v>1224.23</v>
       </c>
       <c r="J30" s="103" t="n"/>
       <c r="K30" s="4" t="n"/>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="H31" s="101" t="n">
-        <v>1224.38</v>
+        <v>1224.23</v>
       </c>
       <c r="I31" s="102" t="n">
-        <v>1224.38</v>
+        <v>1224.23</v>
       </c>
       <c r="J31" s="103" t="n"/>
       <c r="K31" s="4" t="n"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="H32" s="101" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="I32" s="102" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="J32" s="103" t="n"/>
       <c r="K32" s="4" t="n"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="H33" s="101" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="I33" s="102" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="J33" s="103" t="n"/>
       <c r="K33" s="4" t="n"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="H34" s="101" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="I34" s="102" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="J34" s="103" t="n"/>
       <c r="K34" s="4" t="n"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="H35" s="101" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="I35" s="102" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="J35" s="103" t="n"/>
       <c r="K35" s="4" t="n"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="H36" s="101" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="I36" s="102" t="n">
-        <v>790.46</v>
+        <v>790.36</v>
       </c>
       <c r="J36" s="103" t="n"/>
       <c r="K36" s="4" t="n"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="H37" s="101" t="n">
-        <v>665.64</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="I37" s="102" t="n">
-        <v>665.64</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="J37" s="103" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="H38" s="101" t="n">
-        <v>665.64</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="I38" s="102" t="n">
-        <v>665.64</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="J38" s="103" t="n"/>
       <c r="K38" s="4" t="n"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="H39" s="101" t="n">
-        <v>665.64</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="I39" s="102" t="n">
-        <v>665.64</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="J39" s="103" t="n"/>
       <c r="K39" s="4" t="n"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="H40" s="101" t="n">
-        <v>1713.91</v>
+        <v>1713.7</v>
       </c>
       <c r="I40" s="102" t="n">
-        <v>1713.91</v>
+        <v>1713.7</v>
       </c>
       <c r="J40" s="103" t="n"/>
       <c r="K40" s="4" t="n"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="H41" s="101" t="n">
-        <v>2099.61</v>
+        <v>2099.35</v>
       </c>
       <c r="I41" s="102" t="n">
-        <v>2099.61</v>
+        <v>2099.35</v>
       </c>
       <c r="J41" s="103" t="n"/>
       <c r="K41" s="4" t="n"/>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="H42" s="101" t="n">
-        <v>1435.25</v>
+        <v>1435.07</v>
       </c>
       <c r="I42" s="102" t="n">
-        <v>1435.25</v>
+        <v>1435.07</v>
       </c>
       <c r="J42" s="103" t="n"/>
       <c r="K42" s="4" t="n"/>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="H43" s="101" t="n">
-        <v>1952.8</v>
+        <v>1952.56</v>
       </c>
       <c r="I43" s="102" t="n">
-        <v>1952.8</v>
+        <v>1952.56</v>
       </c>
       <c r="J43" s="103" t="n"/>
       <c r="K43" s="4" t="n"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="H44" s="101" t="n">
-        <v>1931.03</v>
+        <v>1930.79</v>
       </c>
       <c r="I44" s="102" t="n">
-        <v>1931.03</v>
+        <v>1930.79</v>
       </c>
       <c r="J44" s="103" t="n"/>
       <c r="K44" s="4" t="n"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="H45" s="101" t="n">
-        <v>1435.25</v>
+        <v>1435.07</v>
       </c>
       <c r="I45" s="102" t="n">
-        <v>1435.25</v>
+        <v>1435.07</v>
       </c>
       <c r="J45" s="103" t="n"/>
       <c r="K45" s="4" t="n"/>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="H46" s="101" t="n">
-        <v>1435.25</v>
+        <v>1435.07</v>
       </c>
       <c r="I46" s="102" t="n">
-        <v>1435.25</v>
+        <v>1435.07</v>
       </c>
       <c r="J46" s="103" t="n"/>
       <c r="K46" s="4" t="n"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="H47" s="101" t="n">
-        <v>2117.3</v>
+        <v>2117.04</v>
       </c>
       <c r="I47" s="102" t="n">
-        <v>2117.3</v>
+        <v>2117.04</v>
       </c>
       <c r="J47" s="103" t="n"/>
       <c r="K47" s="4" t="n"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="H48" s="101" t="n">
-        <v>2122.69</v>
+        <v>2122.43</v>
       </c>
       <c r="I48" s="102" t="n">
-        <v>2122.69</v>
+        <v>2122.43</v>
       </c>
       <c r="J48" s="103" t="n"/>
       <c r="K48" s="4" t="n"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="H49" s="101" t="n">
-        <v>2117.3</v>
+        <v>2117.04</v>
       </c>
       <c r="I49" s="102" t="n">
-        <v>2117.3</v>
+        <v>2117.04</v>
       </c>
       <c r="J49" s="103" t="n"/>
       <c r="K49" s="4" t="n"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="H50" s="101" t="n">
-        <v>1116.04</v>
+        <v>1115.9</v>
       </c>
       <c r="I50" s="102" t="n">
-        <v>1116.04</v>
+        <v>1115.9</v>
       </c>
       <c r="J50" s="103" t="n"/>
       <c r="K50" s="4" t="n"/>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="H51" s="101" t="n">
-        <v>2902.11</v>
+        <v>2901.75</v>
       </c>
       <c r="I51" s="102" t="n">
-        <v>2902.11</v>
+        <v>2901.75</v>
       </c>
       <c r="J51" s="103" t="n"/>
       <c r="K51" s="4" t="n"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="H52" s="101" t="n">
-        <v>1615.64</v>
+        <v>1615.44</v>
       </c>
       <c r="I52" s="102" t="n">
-        <v>1615.64</v>
+        <v>1615.44</v>
       </c>
       <c r="J52" s="103" t="n"/>
       <c r="K52" s="4" t="n"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="H53" s="101" t="n">
-        <v>1865.53</v>
+        <v>1865.31</v>
       </c>
       <c r="I53" s="102" t="n">
-        <v>1865.53</v>
+        <v>1865.31</v>
       </c>
       <c r="J53" s="103" t="n"/>
       <c r="K53" s="4" t="n"/>
@@ -3100,7 +3100,7 @@
       <c r="D54" s="90" t="n"/>
       <c r="E54" s="99" t="inlineStr">
         <is>
-          <t>43 openings</t>
+          <t>43 nr @ GBP 150.00</t>
         </is>
       </c>
       <c r="F54" s="91" t="n">
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="H54" s="86" t="n">
-        <v>3084.28</v>
+        <v>6630.61</v>
       </c>
       <c r="I54" s="88" t="n">
-        <v>3084.28</v>
+        <v>6630.61</v>
       </c>
       <c r="J54" s="93" t="n"/>
       <c r="K54" s="4" t="n"/>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="I57" s="113" t="n">
-        <v>89218.64999999999</v>
+        <v>93526.34</v>
       </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>

--- a/outputs/Redditch Library - Fenster Pricing Document (CLIENT COPY).xlsx
+++ b/outputs/Redditch Library - Fenster Pricing Document (CLIENT COPY).xlsx
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E6" s="10" t="n"/>

--- a/outputs/Redditch Library - Fenster Pricing Document (CLIENT COPY).xlsx
+++ b/outputs/Redditch Library - Fenster Pricing Document (CLIENT COPY).xlsx
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="H9" s="86" t="n">
-        <v>1895.4</v>
+        <v>1933.19</v>
       </c>
       <c r="I9" s="88" t="n">
-        <v>1895.4</v>
+        <v>1933.19</v>
       </c>
       <c r="J9" s="93" t="n"/>
       <c r="K9" s="4" t="n"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="H10" s="86" t="n">
-        <v>1895.4</v>
+        <v>1933.19</v>
       </c>
       <c r="I10" s="88" t="n">
-        <v>1895.4</v>
+        <v>1933.19</v>
       </c>
       <c r="J10" s="93" t="n"/>
       <c r="K10" s="4" t="n"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="H11" s="86" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="I11" s="88" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="J11" s="93" t="n"/>
       <c r="K11" s="4" t="n"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="H12" s="86" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="I12" s="88" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="J12" s="93" t="n"/>
       <c r="K12" s="4" t="n"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="H13" s="86" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="I13" s="88" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="J13" s="93" t="n"/>
       <c r="K13" s="4" t="n"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="H14" s="86" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="I14" s="88" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="J14" s="93" t="n"/>
       <c r="K14" s="4" t="n"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="H15" s="86" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="I15" s="88" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="J15" s="93" t="n"/>
       <c r="K15" s="4" t="n"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="H16" s="86" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="I16" s="88" t="n">
-        <v>2161.46</v>
+        <v>2206.09</v>
       </c>
       <c r="J16" s="93" t="n"/>
       <c r="K16" s="4" t="n"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="H17" s="86" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="I17" s="88" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="J17" s="93" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="H18" s="86" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="I18" s="88" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="J18" s="93" t="n"/>
       <c r="K18" s="4" t="n"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H19" s="86" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="I19" s="88" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="J19" s="93" t="n"/>
       <c r="K19" s="4" t="n"/>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="H20" s="101" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="I20" s="102" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="J20" s="103" t="n"/>
       <c r="K20" s="4" t="n"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="H21" s="101" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="I21" s="102" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="J21" s="103" t="n"/>
       <c r="K21" s="4" t="n"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="H22" s="101" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="I22" s="102" t="n">
-        <v>1894.62</v>
+        <v>1932.4</v>
       </c>
       <c r="J22" s="103" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H23" s="101" t="n">
-        <v>1203.33</v>
+        <v>1225.33</v>
       </c>
       <c r="I23" s="102" t="n">
-        <v>1203.33</v>
+        <v>1225.33</v>
       </c>
       <c r="J23" s="103" t="n"/>
       <c r="K23" s="4" t="n"/>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="H24" s="101" t="n">
-        <v>2249.01</v>
+        <v>2295.88</v>
       </c>
       <c r="I24" s="102" t="n">
-        <v>2249.01</v>
+        <v>2295.88</v>
       </c>
       <c r="J24" s="103" t="n"/>
       <c r="K24" s="4" t="n"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="H25" s="101" t="n">
-        <v>2249.01</v>
+        <v>2295.88</v>
       </c>
       <c r="I25" s="102" t="n">
-        <v>2249.01</v>
+        <v>2295.88</v>
       </c>
       <c r="J25" s="103" t="n"/>
       <c r="K25" s="4" t="n"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="H26" s="101" t="n">
-        <v>2249.01</v>
+        <v>2295.88</v>
       </c>
       <c r="I26" s="102" t="n">
-        <v>2249.01</v>
+        <v>2295.88</v>
       </c>
       <c r="J26" s="103" t="n"/>
       <c r="K26" s="4" t="n"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="H27" s="101" t="n">
-        <v>4550.67</v>
+        <v>4639.5</v>
       </c>
       <c r="I27" s="102" t="n">
-        <v>4550.67</v>
+        <v>4639.5</v>
       </c>
       <c r="J27" s="103" t="n"/>
       <c r="K27" s="4" t="n"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="H28" s="101" t="n">
-        <v>3140.63</v>
+        <v>3199.85</v>
       </c>
       <c r="I28" s="102" t="n">
-        <v>3140.63</v>
+        <v>3199.85</v>
       </c>
       <c r="J28" s="103" t="n"/>
       <c r="K28" s="4" t="n"/>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="H29" s="101" t="n">
-        <v>1203.33</v>
+        <v>1225.33</v>
       </c>
       <c r="I29" s="102" t="n">
-        <v>1203.33</v>
+        <v>1225.33</v>
       </c>
       <c r="J29" s="103" t="n"/>
       <c r="K29" s="4" t="n"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="H30" s="101" t="n">
-        <v>1224.23</v>
+        <v>1246.76</v>
       </c>
       <c r="I30" s="102" t="n">
-        <v>1224.23</v>
+        <v>1246.76</v>
       </c>
       <c r="J30" s="103" t="n"/>
       <c r="K30" s="4" t="n"/>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="H31" s="101" t="n">
-        <v>1224.23</v>
+        <v>1246.76</v>
       </c>
       <c r="I31" s="102" t="n">
-        <v>1224.23</v>
+        <v>1246.76</v>
       </c>
       <c r="J31" s="103" t="n"/>
       <c r="K31" s="4" t="n"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="H32" s="101" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="I32" s="102" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="J32" s="103" t="n"/>
       <c r="K32" s="4" t="n"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="H33" s="101" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="I33" s="102" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="J33" s="103" t="n"/>
       <c r="K33" s="4" t="n"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="H34" s="101" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="I34" s="102" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="J34" s="103" t="n"/>
       <c r="K34" s="4" t="n"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="H35" s="101" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="I35" s="102" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="J35" s="103" t="n"/>
       <c r="K35" s="4" t="n"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="H36" s="101" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="I36" s="102" t="n">
-        <v>790.36</v>
+        <v>801.75</v>
       </c>
       <c r="J36" s="103" t="n"/>
       <c r="K36" s="4" t="n"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="H37" s="101" t="n">
-        <v>665.5599999999999</v>
+        <v>673.73</v>
       </c>
       <c r="I37" s="102" t="n">
-        <v>665.5599999999999</v>
+        <v>673.73</v>
       </c>
       <c r="J37" s="103" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="H38" s="101" t="n">
-        <v>665.5599999999999</v>
+        <v>673.73</v>
       </c>
       <c r="I38" s="102" t="n">
-        <v>665.5599999999999</v>
+        <v>673.73</v>
       </c>
       <c r="J38" s="103" t="n"/>
       <c r="K38" s="4" t="n"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="H39" s="101" t="n">
-        <v>665.5599999999999</v>
+        <v>673.73</v>
       </c>
       <c r="I39" s="102" t="n">
-        <v>665.5599999999999</v>
+        <v>673.73</v>
       </c>
       <c r="J39" s="103" t="n"/>
       <c r="K39" s="4" t="n"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="H40" s="101" t="n">
-        <v>1713.7</v>
+        <v>1746.83</v>
       </c>
       <c r="I40" s="102" t="n">
-        <v>1713.7</v>
+        <v>1746.83</v>
       </c>
       <c r="J40" s="103" t="n"/>
       <c r="K40" s="4" t="n"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="H41" s="101" t="n">
-        <v>2099.35</v>
+        <v>2129.49</v>
       </c>
       <c r="I41" s="102" t="n">
-        <v>2099.35</v>
+        <v>2129.49</v>
       </c>
       <c r="J41" s="103" t="n"/>
       <c r="K41" s="4" t="n"/>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="H42" s="101" t="n">
-        <v>1435.07</v>
+        <v>1463.02</v>
       </c>
       <c r="I42" s="102" t="n">
-        <v>1435.07</v>
+        <v>1463.02</v>
       </c>
       <c r="J42" s="103" t="n"/>
       <c r="K42" s="4" t="n"/>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="H43" s="101" t="n">
-        <v>1952.56</v>
+        <v>1991.82</v>
       </c>
       <c r="I43" s="102" t="n">
-        <v>1952.56</v>
+        <v>1991.82</v>
       </c>
       <c r="J43" s="103" t="n"/>
       <c r="K43" s="4" t="n"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="H44" s="101" t="n">
-        <v>1930.79</v>
+        <v>1956.6</v>
       </c>
       <c r="I44" s="102" t="n">
-        <v>1930.79</v>
+        <v>1956.6</v>
       </c>
       <c r="J44" s="103" t="n"/>
       <c r="K44" s="4" t="n"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="H45" s="101" t="n">
-        <v>1435.07</v>
+        <v>1463.02</v>
       </c>
       <c r="I45" s="102" t="n">
-        <v>1435.07</v>
+        <v>1463.02</v>
       </c>
       <c r="J45" s="103" t="n"/>
       <c r="K45" s="4" t="n"/>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="H46" s="101" t="n">
-        <v>1435.07</v>
+        <v>1463.02</v>
       </c>
       <c r="I46" s="102" t="n">
-        <v>1435.07</v>
+        <v>1463.02</v>
       </c>
       <c r="J46" s="103" t="n"/>
       <c r="K46" s="4" t="n"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="H47" s="101" t="n">
-        <v>2117.04</v>
+        <v>2147.63</v>
       </c>
       <c r="I47" s="102" t="n">
-        <v>2117.04</v>
+        <v>2147.63</v>
       </c>
       <c r="J47" s="103" t="n"/>
       <c r="K47" s="4" t="n"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="H48" s="101" t="n">
-        <v>2122.43</v>
+        <v>2166.06</v>
       </c>
       <c r="I48" s="102" t="n">
-        <v>2122.43</v>
+        <v>2166.06</v>
       </c>
       <c r="J48" s="103" t="n"/>
       <c r="K48" s="4" t="n"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="H49" s="101" t="n">
-        <v>2117.04</v>
+        <v>2147.63</v>
       </c>
       <c r="I49" s="102" t="n">
-        <v>2117.04</v>
+        <v>2147.63</v>
       </c>
       <c r="J49" s="103" t="n"/>
       <c r="K49" s="4" t="n"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="H50" s="101" t="n">
-        <v>1115.9</v>
+        <v>1135.65</v>
       </c>
       <c r="I50" s="102" t="n">
-        <v>1115.9</v>
+        <v>1135.65</v>
       </c>
       <c r="J50" s="103" t="n"/>
       <c r="K50" s="4" t="n"/>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="H51" s="101" t="n">
-        <v>2901.75</v>
+        <v>2936.64</v>
       </c>
       <c r="I51" s="102" t="n">
-        <v>2901.75</v>
+        <v>2936.64</v>
       </c>
       <c r="J51" s="103" t="n"/>
       <c r="K51" s="4" t="n"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="H52" s="101" t="n">
-        <v>1615.44</v>
+        <v>1615.38</v>
       </c>
       <c r="I52" s="102" t="n">
-        <v>1615.44</v>
+        <v>1615.38</v>
       </c>
       <c r="J52" s="103" t="n"/>
       <c r="K52" s="4" t="n"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="H53" s="101" t="n">
-        <v>1865.31</v>
+        <v>1865.24</v>
       </c>
       <c r="I53" s="102" t="n">
-        <v>1865.31</v>
+        <v>1865.24</v>
       </c>
       <c r="J53" s="103" t="n"/>
       <c r="K53" s="4" t="n"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="H54" s="86" t="n">
-        <v>6630.61</v>
+        <v>6630.3</v>
       </c>
       <c r="I54" s="88" t="n">
-        <v>6630.61</v>
+        <v>6630.3</v>
       </c>
       <c r="J54" s="93" t="n"/>
       <c r="K54" s="4" t="n"/>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="I57" s="113" t="n">
-        <v>93526.34</v>
+        <v>94926.75999999999</v>
       </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
